--- a/tools/excel/acn-it/Framework-Nazionale-CS-DP.xlsx
+++ b/tools/excel/acn-it/Framework-Nazionale-CS-DP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\acn-it\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47059D38-AAA8-41E7-BD0D-E3D442649D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB0603D-6EBB-4F58-81A4-B6E4E6D908A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36300" yWindow="-8208" windowWidth="20604" windowHeight="15708" tabRatio="907" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="907" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="607">
   <si>
     <t>type</t>
   </si>
@@ -44,6 +44,9 @@
     <t>version</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>locale</t>
   </si>
   <si>
@@ -59,39 +62,49 @@
     <t>name</t>
   </si>
   <si>
+    <t>Framework Nazionale per la Cybersecurity e la Data Protection (Ed. 2025, v2.1)</t>
+  </si>
+  <si>
     <t>description</t>
   </si>
   <si>
+    <t>Il Framework Nazionale per la Cybersecurity e la Data Protection, nato nel 2015 da una collaborazione sinergica tra accademia, enti pubblici, e imprese private, e successivamente aggiornato nel 2019 a fronte dei requisiti introdotti da GDPR in merito alla protezione dei dati personali, fornisce uno strumento operativo per organizzare i processi di cybersecurity adatto alle organizzazioni pubbliche e private, di qualunque dimensione. 
+https://www.cybersecurityframework.it/
+https://www.acn.gov.it/portale/documents/d/guest/detacn_nis_specifiche_2025_164179_allegato1
+https://www.acn.gov.it/portale/documents/d/guest/detacn_nis_specifiche_2025_164179_allegato2
+Version 2 introduces several fixes and regroups enumeration nodes, which can result in losing corresponding information.</t>
+  </si>
+  <si>
+    <t>copyright</t>
+  </si>
+  <si>
+    <t>ACN</t>
+  </si>
+  <si>
+    <t>provider</t>
+  </si>
+  <si>
+    <t>packager</t>
+  </si>
+  <si>
+    <t>matteo.palli</t>
+  </si>
+  <si>
+    <t>framework</t>
+  </si>
+  <si>
+    <t>base_urn</t>
+  </si>
+  <si>
+    <t>urn:intuitem:risk:req_node:Framework-Nazionale-C-DP</t>
+  </si>
+  <si>
+    <t>urn:intuitem:risk:framework:Framework-Nazionale-C-DP</t>
+  </si>
+  <si>
     <t>Il Framework Nazionale per la Cybersecurity e la Data Protection, nato nel 2015 da una collaborazione sinergica tra accademia, enti pubblici, e imprese private, e successivamente aggiornato nel 2019 a fronte dei requisiti introdotti da GDPR in merito alla protezione dei dati personali, fornisce uno strumento operativo per organizzare i processi di cybersecurity adatto alle organizzazioni pubbliche e private, di qualunque dimensione. https://www.cybersecurityframework.it/</t>
   </si>
   <si>
-    <t>copyright</t>
-  </si>
-  <si>
-    <t>ACN</t>
-  </si>
-  <si>
-    <t>provider</t>
-  </si>
-  <si>
-    <t>packager</t>
-  </si>
-  <si>
-    <t>matteo.palli</t>
-  </si>
-  <si>
-    <t>framework</t>
-  </si>
-  <si>
-    <t>base_urn</t>
-  </si>
-  <si>
-    <t>urn:intuitem:risk:req_node:Framework-Nazionale-C-DP</t>
-  </si>
-  <si>
-    <t>urn:intuitem:risk:framework:Framework-Nazionale-C-DP</t>
-  </si>
-  <si>
     <t>implementation_groups_definition</t>
   </si>
   <si>
@@ -152,6 +165,9 @@
     <t>Gli obiettivi, le capacità e i servizi critici dai quali gli stakeholder dipendono o che si aspettano dall'organizzazione sono compresi e comunicati.</t>
   </si>
   <si>
+    <t>I,E,CONTROLLI,ICONT,ECONT</t>
+  </si>
+  <si>
     <t>GV.OC-04.1</t>
   </si>
   <si>
@@ -296,7 +312,7 @@
     <t>Nel rispetto delle politiche di cui alla misura GV.PO-01, sono adottate e documentate le procedure in relazione ai punti GV.RR-04.1 e GV.RR-04.2.</t>
   </si>
   <si>
-    <t>E</t>
+    <t>E,CONTROLLI,ECONT</t>
   </si>
   <si>
     <t>GV.RR-04.4</t>
@@ -333,6 +349,25 @@
   </si>
   <si>
     <t>GV.PO-01.1</t>
+  </si>
+  <si>
+    <t>Sono adottate e documentate politiche di sicurezza informatica per almeno i seguenti ambiti:
+a) gestione del rischio;
+b) ruoli e responsabilità;
+c) affidabilità delle risorse umane;
+d) conformità e audit di sicurezza;
+e) gestione dei rischi per la sicurezza informatica della catena di approvvigionamento;
+f) gestione degli asset;
+g) gestione delle vulnerabilità;
+h) continuità operativa, ripristino in caso di disastro e gestione delle crisi;
+i) gestione dell'autenticazione, delle identità digitali e del controllo accessi;
+j) sicurezza fisica;
+k) formazione del personale e consapevolezza;
+l) sicurezza dei dati;
+m) sviluppo, configurazione, manutenzione e dismissione dei sistemi informativi e di rete;
+n) protezione delle reti e delle comunicazioni;
+o) monitoraggio degli eventi di sicurezza;
+p) risposta agli incidenti e ripristino.</t>
   </si>
   <si>
     <t>GV.PO-01.2</t>
@@ -1600,239 +1635,6 @@
     <t>RS.MA-01.1</t>
   </si>
   <si>
-    <t>RS.MA-01.2</t>
-  </si>
-  <si>
-    <t>Il piano di cui al punto RS.MA-01.1 è approvato dagli organi di amministrazione e direttivi.</t>
-  </si>
-  <si>
-    <t>RS.MA-01.3</t>
-  </si>
-  <si>
-    <t>Il piano di cui al punto RS.MA-01.1 è riesaminato e, se opportuno, aggiornato periodicamente e comunque almeno ogni due anni, nonché qualora si verifichino incidenti significativi, integrando le relative lezioni apprese, o mutamenti dell’esposizione alle minacce e ai relativi rischi.</t>
-  </si>
-  <si>
-    <t>RS.MA-02</t>
-  </si>
-  <si>
-    <t>I report sugli incidenti sono sottoposti a triage e convalidati.</t>
-  </si>
-  <si>
-    <t>RS.MA-03</t>
-  </si>
-  <si>
-    <t>Gli incidenti sono categorizzati e prioritizzati.</t>
-  </si>
-  <si>
-    <t>RS.MA-04</t>
-  </si>
-  <si>
-    <t>Gli incidenti sono scalati (assegnati a meccanismi di risposta con risorse crescenti) o elevati (passati in gestione a un livello superiore) a seconda delle necessità.</t>
-  </si>
-  <si>
-    <t>RS.MA-05</t>
-  </si>
-  <si>
-    <t>Sono applicati i criteri per l'avvio del ripristino dagli incidenti.</t>
-  </si>
-  <si>
-    <t>RS.AN</t>
-  </si>
-  <si>
-    <t>Analisi degli incidenti</t>
-  </si>
-  <si>
-    <t>Sono condotte indagini per garantire una risposta efficace e supportare le attività forensi e di ripristino.</t>
-  </si>
-  <si>
-    <t>RS.AN-03</t>
-  </si>
-  <si>
-    <t>È eseguita un'analisi per stabilire cosa è avvenuto durante un incidente e la causa principale dell'incidente.</t>
-  </si>
-  <si>
-    <t>RS.AN-06</t>
-  </si>
-  <si>
-    <t>Le azioni eseguite durante un'investigazione sono registrate e l'integrità e la provenienza delle registrazioni sono preservate.</t>
-  </si>
-  <si>
-    <t>RS.AN-07</t>
-  </si>
-  <si>
-    <t>I dati e i metadati degli incidenti sono raccolti e la loro integrità e provenienza sono preservate.</t>
-  </si>
-  <si>
-    <t>RS.AN-08</t>
-  </si>
-  <si>
-    <t>La magnitudo di un incidente è stimata e convalidata.</t>
-  </si>
-  <si>
-    <t>RS.CO</t>
-  </si>
-  <si>
-    <t>Segnalazione e comunicazione della risposta agli incidenti</t>
-  </si>
-  <si>
-    <t>Le attività di risposta sono coordinate con gli stakeholder interni ed esterni come richiesto da leggi, regolamenti o politiche.</t>
-  </si>
-  <si>
-    <t>RS.CO-02</t>
-  </si>
-  <si>
-    <t>Gli stakeholder interni ed esterni sono informati degli incidenti.</t>
-  </si>
-  <si>
-    <t>RS.CO-02.1</t>
-  </si>
-  <si>
-    <t>In accordo al piano per la gestione degli incidenti di cui alla misura RS.MA-01, sono documentate e adottate procedure per comunicare senza ingiustificato ritardo, se ritenuto opportuno e qualora possibile, sentito il CSIRT Italia, ovvero qualora intimato dall’Agenzia per la cybersicurezza nazionale ai sensi dell’articolo 37, comma 3, lettere g) e h), del decreto NIS:
-a) ai destinatari dei loro servizi, gli incidenti significativi che possono ripercuotersi negativamente sulla fornitura di tali servizi;
-b) ai destinatari dei servizi che sono potenzialmente interessati da una minaccia informatica significativa, le misure o azioni correttive o di mitigazione che tali destinatari possono adottare in risposta a tale minaccia e la natura di tale minaccia.</t>
-  </si>
-  <si>
-    <t>RS.CO-02.2</t>
-  </si>
-  <si>
-    <t>Sono documentate e adottate procedure per informare il pubblico sugli incidenti occorsi, qualora intimato dall’Agenzia per la cybersicurezza nazionale ai sensi dell’art. 37, comma 3, lettera i) del decreto NIS.</t>
-  </si>
-  <si>
-    <t>RS.CO-03</t>
-  </si>
-  <si>
-    <t>Le informazioni sono condivise con gli stakeholder interni ed esterni designati.</t>
-  </si>
-  <si>
-    <t>DP-RS.CO-06</t>
-  </si>
-  <si>
-    <t>Gli incidenti che si configurano come violazioni di dati personali sono documentati ed eventualmente vengono informate le autorità di riferimento e gli interessati.</t>
-  </si>
-  <si>
-    <t>RS.MI</t>
-  </si>
-  <si>
-    <t>Mitigazione degli incidenti</t>
-  </si>
-  <si>
-    <t>Sono eseguite attività per prevenire l'espansione di un evento e mitigarne gli effetti.</t>
-  </si>
-  <si>
-    <t>RS.MI-01</t>
-  </si>
-  <si>
-    <t>Gli incidenti vengono contenuti.</t>
-  </si>
-  <si>
-    <t>RS.MI-02</t>
-  </si>
-  <si>
-    <t>Gli incidenti vengono eradicati.</t>
-  </si>
-  <si>
-    <t>RC</t>
-  </si>
-  <si>
-    <t>RECOVER</t>
-  </si>
-  <si>
-    <t>Gli asset e le operazioni interessati da un incidente di cybersecurity sono ripristinati.</t>
-  </si>
-  <si>
-    <t>RC.RP</t>
-  </si>
-  <si>
-    <t>Esecuzione del piano di ripristino dagli incidenti</t>
-  </si>
-  <si>
-    <t>Le attività di ripristino sono eseguite per garantire la disponibilità operativa dei sistemi e dei servizi interessati da incidenti di cybersecurity.</t>
-  </si>
-  <si>
-    <t>RC.RP-01</t>
-  </si>
-  <si>
-    <t>La parte del piano di risposta agli incidenti relativa al rispristino viene eseguita una volta avviata dal processo di risposta agli incidenti.</t>
-  </si>
-  <si>
-    <t>RC.RP-01.1</t>
-  </si>
-  <si>
-    <t>Nell'ambito del piano per la gestione degli incidenti di cui alla misura RS.MA-01, sono adottate e documentate procedure per il ripristino con riguardo almeno al ripristino del normale funzionamento dei sistemi informativi e di rete coinvolti da incidenti di sicurezza informatica, ivi compresi quelli di cui all’articolo 25 del decreto NIS.</t>
-  </si>
-  <si>
-    <t>RC.RP-02</t>
-  </si>
-  <si>
-    <t>Le azioni di ripristino sono selezionate, contestualizzate, prioritizzate e eseguite.</t>
-  </si>
-  <si>
-    <t>RC.RP-03</t>
-  </si>
-  <si>
-    <t>L'integrità dei backup e delle altre risorse di ripristino è verificata prima che siano utilizzati per il ripristino.</t>
-  </si>
-  <si>
-    <t>Sono adottate e documentate procedure per comunicare alle parti interne interessate, ivi incluse le articolazioni competenti del soggetto NIS, le attività di ripristino a seguito di un incidente.</t>
-  </si>
-  <si>
-    <t>RC.RP-04</t>
-  </si>
-  <si>
-    <t>Le funzioni critiche per la mission dell'organizzazione e la gestione del rischio di cybersecurity sono considerate per stabilire le norme operative post-incidente.</t>
-  </si>
-  <si>
-    <t>RC.RP-05</t>
-  </si>
-  <si>
-    <t>L'integrità degli asset ripristinati è verificata, i sistemi e i servizi sono ripristinati e lo stato operativo normale viene confermato.</t>
-  </si>
-  <si>
-    <t>RC.RP-06</t>
-  </si>
-  <si>
-    <t>La conclusione del ripristino dell'incidente viene dichiarata sulla base di criteri definiti e la documentazione relativa all'incidente è completata.</t>
-  </si>
-  <si>
-    <t>RC.CO</t>
-  </si>
-  <si>
-    <t>Comunicazione sul ripristino dagli incidenti</t>
-  </si>
-  <si>
-    <t>Le attività di ripristino sono coordinate con le parti interne ed esterne.</t>
-  </si>
-  <si>
-    <t>RC.CO-03</t>
-  </si>
-  <si>
-    <t>Le attività di ripristino e i progressi nel ripristino delle capacità operative sono comunicati agli stakeholder interni ed esterni designati.</t>
-  </si>
-  <si>
-    <t>RC.CO-04</t>
-  </si>
-  <si>
-    <t>Gli aggiornamenti pubblici sul ripristino dagli incidenti sono condivisi utilizzando modalità e messaggi approvati.</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>Importanti</t>
-  </si>
-  <si>
-    <t>Misure di sicurezza di base per i soggetti importanti</t>
-  </si>
-  <si>
-    <t>Essenziali</t>
-  </si>
-  <si>
-    <t>Misure di sicurezza di base per i soggetti essenziali</t>
-  </si>
-  <si>
-    <t>RC.CO-03.1</t>
-  </si>
-  <si>
     <t>È definito, attuato, aggiornato e documentato un piano per la gestione degli incidenti di sicurezza informatica e la notifica al CSIRT Italia, in accordo a quanto previsto dall’articolo 25 del decreto NIS, che comprende almeno:
 a) le fasi e le procedure di gestione e notifica degli incidenti con l’indicazione dei relativi ruoli e delle responsabilità;
 b) le procedure per la predisposizione e la trasmissione delle relazioni di cui all’articolo 25, comma 5, lettere c), d) ed e) del decreto NIS;
@@ -1841,30 +1643,243 @@
 e) la reportistica da utilizzare per la documentazione dell’incidente.</t>
   </si>
   <si>
-    <t>Sono adottate e documentate politiche di sicurezza informatica per almeno i seguenti ambiti:
-a) gestione del rischio;
-b) ruoli e responsabilità;
-c) affidabilità delle risorse umane;
-d) conformità e audit di sicurezza;
-e) gestione dei rischi per la sicurezza informatica della catena di approvvigionamento;
-f) gestione degli asset;
-g) gestione delle vulnerabilità;
-h) continuità operativa, ripristino in caso di disastro e gestione delle crisi;
-i) gestione dell'autenticazione, delle identità digitali e del controllo accessi;
-j) sicurezza fisica;
-k) formazione del personale e consapevolezza;
-l) sicurezza dei dati;
-m) sviluppo, configurazione, manutenzione e dismissione dei sistemi informativi e di rete;
-n) protezione delle reti e delle comunicazioni;
-o) monitoraggio degli eventi di sicurezza;
-p) risposta agli incidenti e ripristino.</t>
-  </si>
-  <si>
-    <t>Il Framework Nazionale per la Cybersecurity e la Data Protection, nato nel 2015 da una collaborazione sinergica tra accademia, enti pubblici, e imprese private, e successivamente aggiornato nel 2019 a fronte dei requisiti introdotti da GDPR in merito alla protezione dei dati personali, fornisce uno strumento operativo per organizzare i processi di cybersecurity adatto alle organizzazioni pubbliche e private, di qualunque dimensione. 
-https://www.cybersecurityframework.it/
-https://www.acn.gov.it/portale/documents/d/guest/detacn_nis_specifiche_2025_164179_allegato1
-https://www.acn.gov.it/portale/documents/d/guest/detacn_nis_specifiche_2025_164179_allegato2
-Version 2 introduces several fixes and regroups enumeration nodes, which can result in losing corresponding information.</t>
+    <t>RS.MA-01.2</t>
+  </si>
+  <si>
+    <t>Il piano di cui al punto RS.MA-01.1 è approvato dagli organi di amministrazione e direttivi.</t>
+  </si>
+  <si>
+    <t>RS.MA-01.3</t>
+  </si>
+  <si>
+    <t>Il piano di cui al punto RS.MA-01.1 è riesaminato e, se opportuno, aggiornato periodicamente e comunque almeno ogni due anni, nonché qualora si verifichino incidenti significativi, integrando le relative lezioni apprese, o mutamenti dell’esposizione alle minacce e ai relativi rischi.</t>
+  </si>
+  <si>
+    <t>RS.MA-02</t>
+  </si>
+  <si>
+    <t>I report sugli incidenti sono sottoposti a triage e convalidati.</t>
+  </si>
+  <si>
+    <t>RS.MA-03</t>
+  </si>
+  <si>
+    <t>Gli incidenti sono categorizzati e prioritizzati.</t>
+  </si>
+  <si>
+    <t>RS.MA-04</t>
+  </si>
+  <si>
+    <t>Gli incidenti sono scalati (assegnati a meccanismi di risposta con risorse crescenti) o elevati (passati in gestione a un livello superiore) a seconda delle necessità.</t>
+  </si>
+  <si>
+    <t>RS.MA-05</t>
+  </si>
+  <si>
+    <t>Sono applicati i criteri per l'avvio del ripristino dagli incidenti.</t>
+  </si>
+  <si>
+    <t>RS.AN</t>
+  </si>
+  <si>
+    <t>Analisi degli incidenti</t>
+  </si>
+  <si>
+    <t>Sono condotte indagini per garantire una risposta efficace e supportare le attività forensi e di ripristino.</t>
+  </si>
+  <si>
+    <t>RS.AN-03</t>
+  </si>
+  <si>
+    <t>È eseguita un'analisi per stabilire cosa è avvenuto durante un incidente e la causa principale dell'incidente.</t>
+  </si>
+  <si>
+    <t>RS.AN-06</t>
+  </si>
+  <si>
+    <t>Le azioni eseguite durante un'investigazione sono registrate e l'integrità e la provenienza delle registrazioni sono preservate.</t>
+  </si>
+  <si>
+    <t>RS.AN-07</t>
+  </si>
+  <si>
+    <t>I dati e i metadati degli incidenti sono raccolti e la loro integrità e provenienza sono preservate.</t>
+  </si>
+  <si>
+    <t>RS.AN-08</t>
+  </si>
+  <si>
+    <t>La magnitudo di un incidente è stimata e convalidata.</t>
+  </si>
+  <si>
+    <t>RS.CO</t>
+  </si>
+  <si>
+    <t>Segnalazione e comunicazione della risposta agli incidenti</t>
+  </si>
+  <si>
+    <t>Le attività di risposta sono coordinate con gli stakeholder interni ed esterni come richiesto da leggi, regolamenti o politiche.</t>
+  </si>
+  <si>
+    <t>RS.CO-02</t>
+  </si>
+  <si>
+    <t>Gli stakeholder interni ed esterni sono informati degli incidenti.</t>
+  </si>
+  <si>
+    <t>RS.CO-02.1</t>
+  </si>
+  <si>
+    <t>In accordo al piano per la gestione degli incidenti di cui alla misura RS.MA-01, sono documentate e adottate procedure per comunicare senza ingiustificato ritardo, se ritenuto opportuno e qualora possibile, sentito il CSIRT Italia, ovvero qualora intimato dall’Agenzia per la cybersicurezza nazionale ai sensi dell’articolo 37, comma 3, lettere g) e h), del decreto NIS:
+a) ai destinatari dei loro servizi, gli incidenti significativi che possono ripercuotersi negativamente sulla fornitura di tali servizi;
+b) ai destinatari dei servizi che sono potenzialmente interessati da una minaccia informatica significativa, le misure o azioni correttive o di mitigazione che tali destinatari possono adottare in risposta a tale minaccia e la natura di tale minaccia.</t>
+  </si>
+  <si>
+    <t>RS.CO-02.2</t>
+  </si>
+  <si>
+    <t>Sono documentate e adottate procedure per informare il pubblico sugli incidenti occorsi, qualora intimato dall’Agenzia per la cybersicurezza nazionale ai sensi dell’art. 37, comma 3, lettera i) del decreto NIS.</t>
+  </si>
+  <si>
+    <t>RS.CO-03</t>
+  </si>
+  <si>
+    <t>Le informazioni sono condivise con gli stakeholder interni ed esterni designati.</t>
+  </si>
+  <si>
+    <t>DP-RS.CO-06</t>
+  </si>
+  <si>
+    <t>Gli incidenti che si configurano come violazioni di dati personali sono documentati ed eventualmente vengono informate le autorità di riferimento e gli interessati.</t>
+  </si>
+  <si>
+    <t>RS.MI</t>
+  </si>
+  <si>
+    <t>Mitigazione degli incidenti</t>
+  </si>
+  <si>
+    <t>Sono eseguite attività per prevenire l'espansione di un evento e mitigarne gli effetti.</t>
+  </si>
+  <si>
+    <t>RS.MI-01</t>
+  </si>
+  <si>
+    <t>Gli incidenti vengono contenuti.</t>
+  </si>
+  <si>
+    <t>RS.MI-02</t>
+  </si>
+  <si>
+    <t>Gli incidenti vengono eradicati.</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>RECOVER</t>
+  </si>
+  <si>
+    <t>Gli asset e le operazioni interessati da un incidente di cybersecurity sono ripristinati.</t>
+  </si>
+  <si>
+    <t>RC.RP</t>
+  </si>
+  <si>
+    <t>Esecuzione del piano di ripristino dagli incidenti</t>
+  </si>
+  <si>
+    <t>Le attività di ripristino sono eseguite per garantire la disponibilità operativa dei sistemi e dei servizi interessati da incidenti di cybersecurity.</t>
+  </si>
+  <si>
+    <t>RC.RP-01</t>
+  </si>
+  <si>
+    <t>La parte del piano di risposta agli incidenti relativa al rispristino viene eseguita una volta avviata dal processo di risposta agli incidenti.</t>
+  </si>
+  <si>
+    <t>RC.RP-01.1</t>
+  </si>
+  <si>
+    <t>Nell'ambito del piano per la gestione degli incidenti di cui alla misura RS.MA-01, sono adottate e documentate procedure per il ripristino con riguardo almeno al ripristino del normale funzionamento dei sistemi informativi e di rete coinvolti da incidenti di sicurezza informatica, ivi compresi quelli di cui all’articolo 25 del decreto NIS.</t>
+  </si>
+  <si>
+    <t>RC.RP-02</t>
+  </si>
+  <si>
+    <t>Le azioni di ripristino sono selezionate, contestualizzate, prioritizzate e eseguite.</t>
+  </si>
+  <si>
+    <t>RC.RP-03</t>
+  </si>
+  <si>
+    <t>L'integrità dei backup e delle altre risorse di ripristino è verificata prima che siano utilizzati per il ripristino.</t>
+  </si>
+  <si>
+    <t>RC.RP-04</t>
+  </si>
+  <si>
+    <t>Le funzioni critiche per la mission dell'organizzazione e la gestione del rischio di cybersecurity sono considerate per stabilire le norme operative post-incidente.</t>
+  </si>
+  <si>
+    <t>RC.RP-05</t>
+  </si>
+  <si>
+    <t>L'integrità degli asset ripristinati è verificata, i sistemi e i servizi sono ripristinati e lo stato operativo normale viene confermato.</t>
+  </si>
+  <si>
+    <t>RC.RP-06</t>
+  </si>
+  <si>
+    <t>La conclusione del ripristino dell'incidente viene dichiarata sulla base di criteri definiti e la documentazione relativa all'incidente è completata.</t>
+  </si>
+  <si>
+    <t>RC.CO</t>
+  </si>
+  <si>
+    <t>Comunicazione sul ripristino dagli incidenti</t>
+  </si>
+  <si>
+    <t>Le attività di ripristino sono coordinate con le parti interne ed esterne.</t>
+  </si>
+  <si>
+    <t>RC.CO-03</t>
+  </si>
+  <si>
+    <t>Le attività di ripristino e i progressi nel ripristino delle capacità operative sono comunicati agli stakeholder interni ed esterni designati.</t>
+  </si>
+  <si>
+    <t>RC.CO-03.1</t>
+  </si>
+  <si>
+    <t>Sono adottate e documentate procedure per comunicare alle parti interne interessate, ivi incluse le articolazioni competenti del soggetto NIS, le attività di ripristino a seguito di un incidente.</t>
+  </si>
+  <si>
+    <t>RC.CO-04</t>
+  </si>
+  <si>
+    <t>Gli aggiornamenti pubblici sul ripristino dagli incidenti sono condivisi utilizzando modalità e messaggi approvati.</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Importanti</t>
+  </si>
+  <si>
+    <t>Misure di sicurezza di base per i soggetti importanti</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Essenziali</t>
+  </si>
+  <si>
+    <t>Misure di sicurezza di base per i soggetti essenziali</t>
+  </si>
+  <si>
+    <t>REQ</t>
   </si>
   <si>
     <t>CONTROLLI</t>
@@ -1873,35 +1888,59 @@
     <t>Controlli</t>
   </si>
   <si>
-    <t>REQ</t>
-  </si>
-  <si>
-    <t>Requisito</t>
-  </si>
-  <si>
-    <t>I,E,CONTROLLI</t>
-  </si>
-  <si>
-    <t>E,CONTROLLI</t>
-  </si>
-  <si>
-    <t>E,REQ</t>
-  </si>
-  <si>
-    <t>I,E,REQ</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Framework Nazionale per la Cybersecurity e la Data Protection (Ed. 2025, v2.1)</t>
+    <t>CONT</t>
+  </si>
+  <si>
+    <t>IREQ</t>
+  </si>
+  <si>
+    <t>EREQ</t>
+  </si>
+  <si>
+    <t>ICONT</t>
+  </si>
+  <si>
+    <t>ECONT</t>
+  </si>
+  <si>
+    <t>Requisiti importanti</t>
+  </si>
+  <si>
+    <t>Requisiti essenziali</t>
+  </si>
+  <si>
+    <t>Controlli importanti</t>
+  </si>
+  <si>
+    <t>Controlli essenziali</t>
+  </si>
+  <si>
+    <t>Requisiti non NIS</t>
+  </si>
+  <si>
+    <t>Requisiti</t>
+  </si>
+  <si>
+    <t>REQUISITI</t>
+  </si>
+  <si>
+    <t>REQUISITI,REQ</t>
+  </si>
+  <si>
+    <t>I,E,REQUISITI,IREQ,EREQ</t>
+  </si>
+  <si>
+    <t>E,REQUISITI,EREQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No CONT because every controls are either E or I,E </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1918,6 +1957,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1970,7 +2024,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1988,6 +2042,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2318,63 +2374,63 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>592</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>583</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2396,15 +2452,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -2412,39 +2468,39 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2459,7 +2515,7 @@
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="146" customWidth="1"/>
@@ -2469,22 +2525,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2492,13 +2548,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2506,115 +2562,115 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B4" s="4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B5" s="4">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B9" s="4">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2622,149 +2678,149 @@
         <v>2</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B11" s="4">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B12" s="4">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B13" s="4">
         <v>3</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B14" s="4">
         <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B15" s="4">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B17" s="4">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B18" s="4">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2772,251 +2828,251 @@
         <v>2</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B20" s="4">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B21" s="4">
         <v>3</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B22" s="4">
         <v>4</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B23" s="4">
         <v>4</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B24" s="4">
         <v>4</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B25" s="4">
         <v>4</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B27" s="4">
         <v>3</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B28" s="4">
         <v>4</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B29" s="4">
         <v>4</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B30" s="4">
         <v>4</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B31" s="4">
         <v>4</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B32" s="4">
         <v>4</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B33" s="4">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3024,146 +3080,149 @@
         <v>2</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B35" s="4">
         <v>3</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="244.8" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
       <c r="B36" s="4">
         <v>4</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>582</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B37" s="4">
         <v>4</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B38" s="4">
         <v>4</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B39" s="4">
         <v>3</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B40" s="4">
         <v>4</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B41" s="4">
         <v>4</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B42" s="4">
         <v>4</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3171,64 +3230,64 @@
         <v>2</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B44" s="4">
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B45" s="4">
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B46" s="4">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -3236,319 +3295,319 @@
         <v>2</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B48" s="4">
         <v>3</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B49" s="4">
         <v>4</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="319.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B50">
         <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D50" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B51" s="4">
         <v>3</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B52" s="4">
         <v>4</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B53" s="4">
         <v>4</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B54" s="4">
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B55" s="4">
         <v>3</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B56" s="4">
         <v>4</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B57" s="4">
         <v>3</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B58" s="4">
         <v>4</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B59" s="4">
         <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B60" s="4">
         <v>3</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B61" s="4">
         <v>4</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B62" s="4">
         <v>4</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B63" s="4">
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B64" s="4">
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B65" s="4">
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3556,13 +3615,13 @@
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3570,217 +3629,217 @@
         <v>2</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B68" s="4">
         <v>3</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B69" s="4">
         <v>4</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B70" s="4">
         <v>3</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B71" s="4">
         <v>4</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B72" s="4">
         <v>3</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B73" s="4">
         <v>4</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B74" s="4">
         <v>3</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B75" s="4">
         <v>4</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B76" s="4">
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B77" s="4">
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B78" s="4">
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B79" s="4">
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3788,455 +3847,455 @@
         <v>2</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B81" s="4">
         <v>3</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B82" s="4">
         <v>4</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B83" s="4">
         <v>4</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B84" s="4">
         <v>4</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B85" s="4">
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B86" s="4">
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B87" s="4">
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B88" s="4">
         <v>3</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B89" s="4">
         <v>4</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B90" s="4">
         <v>4</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B91" s="4">
         <v>4</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B92" s="4">
         <v>4</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B93" s="4">
         <v>3</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B94" s="4">
         <v>4</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B95" s="4">
         <v>4</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B96" s="4">
         <v>4</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B97" s="4">
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B98" s="4">
         <v>3</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B99" s="4">
         <v>4</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B100" s="4">
         <v>4</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B101" s="4">
         <v>4</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B102" s="4">
         <v>4</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B103" s="4">
         <v>4</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B104" s="4">
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B105" s="4">
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B106" s="4">
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4244,234 +4303,234 @@
         <v>2</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B108" s="4">
         <v>3</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B109" s="4">
         <v>4</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B110" s="4">
         <v>4</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B111" s="4">
         <v>4</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B112" s="4">
         <v>4</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B113" s="4">
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B114" s="4">
         <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B115" s="4">
         <v>3</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B116" s="4">
         <v>4</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="127.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B117" s="4">
         <v>4</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B118" s="4">
         <v>4</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B119" s="4">
         <v>4</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B120" s="4">
         <v>4</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4479,98 +4538,98 @@
         <v>2</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B122" s="4">
         <v>3</v>
       </c>
       <c r="C122" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B123" s="4">
         <v>3</v>
       </c>
       <c r="C123" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B124" s="4">
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B125" s="4">
         <v>3</v>
       </c>
       <c r="C125" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B126" s="4">
         <v>3</v>
       </c>
       <c r="C126" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4578,13 +4637,13 @@
         <v>1</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -4592,319 +4651,319 @@
         <v>2</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B129" s="4">
         <v>3</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B130" s="4">
         <v>4</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B131" s="4">
         <v>4</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B132" s="4">
         <v>4</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B133" s="4">
         <v>4</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B134" s="4">
         <v>3</v>
       </c>
       <c r="C134" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B135" s="4">
         <v>3</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B136" s="4">
         <v>4</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B137" s="4">
         <v>4</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B138" s="4">
         <v>4</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B139" s="4">
         <v>3</v>
       </c>
       <c r="C139" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B140" s="4">
         <v>3</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B141" s="4">
         <v>4</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B142" s="4">
         <v>4</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B143" s="4">
         <v>4</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B144" s="4">
         <v>3</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B145" s="4">
         <v>4</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B146" s="4">
         <v>4</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4912,132 +4971,132 @@
         <v>2</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B148" s="4">
         <v>3</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B149" s="4">
         <v>4</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B150" s="4">
         <v>4</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B151" s="4">
         <v>4</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B152" s="4">
         <v>3</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B153" s="4">
         <v>4</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B154" s="4">
         <v>4</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5045,251 +5104,251 @@
         <v>2</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B156" s="4">
         <v>3</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B157" s="4">
         <v>4</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B158" s="4">
         <v>4</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B159" s="4">
         <v>4</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B160" s="4">
         <v>3</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B161" s="4">
         <v>4</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B162" s="4">
         <v>4</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B163" s="4">
         <v>3</v>
       </c>
       <c r="C163" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B164" s="4">
         <v>3</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B165" s="4">
         <v>4</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B166" s="4">
         <v>4</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B167" s="4">
         <v>4</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B168" s="4">
         <v>4</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B169" s="4">
         <v>4</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5297,353 +5356,353 @@
         <v>2</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B171" s="4">
         <v>3</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B172" s="4">
         <v>4</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B173" s="4">
         <v>4</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B174" s="4">
         <v>3</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B175" s="4">
         <v>4</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B176" s="4">
         <v>4</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B177" s="4">
         <v>4</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B178" s="4">
         <v>4</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B179" s="4">
         <v>4</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B180" s="4">
         <v>3</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B181" s="4">
         <v>4</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B182" s="4">
         <v>4</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B183" s="4">
         <v>3</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B184" s="4">
         <v>4</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B185" s="4">
         <v>4</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B186" s="4">
         <v>4</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B187" s="4">
         <v>4</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B188" s="4">
         <v>3</v>
       </c>
       <c r="C188" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B189" s="4">
         <v>3</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B190" s="4">
         <v>4</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5651,183 +5710,183 @@
         <v>2</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B192" s="4">
         <v>3</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B193" s="4">
         <v>4</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B194" s="4">
         <v>4</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B195" s="4">
         <v>4</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B196" s="4">
         <v>4</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B197" s="4">
         <v>3</v>
       </c>
       <c r="C197" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B198" s="4">
         <v>3</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B199" s="4">
         <v>4</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B200" s="4">
         <v>4</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B201" s="4">
         <v>3</v>
       </c>
       <c r="C201" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5835,13 +5894,13 @@
         <v>1</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5849,251 +5908,251 @@
         <v>2</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B204" s="4">
         <v>3</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B205" s="4">
         <v>4</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B206" s="4">
         <v>4</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B207" s="4">
         <v>4</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B208" s="4">
         <v>4</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B209" s="4">
         <v>4</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B210" s="4">
         <v>4</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B211" s="4">
         <v>4</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B212" s="4">
         <v>3</v>
       </c>
       <c r="C212" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B213" s="4">
         <v>3</v>
       </c>
       <c r="C213" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B214" s="4">
         <v>3</v>
       </c>
       <c r="C214" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B215" s="4">
         <v>3</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B216" s="4">
         <v>4</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B217" s="4">
         <v>4</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6101,115 +6160,115 @@
         <v>2</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B219" s="4">
         <v>3</v>
       </c>
       <c r="C219" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B220" s="4">
         <v>3</v>
       </c>
       <c r="C220" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B221" s="4">
         <v>3</v>
       </c>
       <c r="C221" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B222" s="4">
         <v>3</v>
       </c>
       <c r="C222" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B223" s="4">
         <v>3</v>
       </c>
       <c r="C223" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B224" s="4">
         <v>3</v>
       </c>
       <c r="C224" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6217,13 +6276,13 @@
         <v>1</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6231,149 +6290,149 @@
         <v>2</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B227" s="4">
         <v>3</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="130.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B228" s="4">
         <v>4</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>581</v>
+        <v>509</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B229" s="4">
         <v>4</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B230" s="4">
         <v>4</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B231" s="4">
         <v>3</v>
       </c>
       <c r="C231" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B232" s="4">
         <v>3</v>
       </c>
       <c r="C232" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B233" s="4">
         <v>3</v>
       </c>
       <c r="C233" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B234" s="4">
         <v>3</v>
       </c>
       <c r="C234" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6381,81 +6440,81 @@
         <v>2</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="236" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B236" s="4">
         <v>3</v>
       </c>
       <c r="C236" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B237" s="4">
         <v>3</v>
       </c>
       <c r="C237" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B238" s="4">
         <v>3</v>
       </c>
       <c r="C238" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="239" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B239" s="4">
         <v>3</v>
       </c>
       <c r="C239" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6463,98 +6522,98 @@
         <v>2</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="241" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B241" s="4">
         <v>3</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="242" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B242" s="4">
         <v>4</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B243" s="4">
         <v>4</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B244" s="4">
         <v>3</v>
       </c>
       <c r="C244" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="245" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B245" s="4">
         <v>3</v>
       </c>
       <c r="C245" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="246" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6562,47 +6621,47 @@
         <v>2</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B247" s="4">
         <v>3</v>
       </c>
       <c r="C247" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B248" s="4">
         <v>3</v>
       </c>
       <c r="C248" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="249" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6610,13 +6669,13 @@
         <v>1</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="250" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6624,132 +6683,132 @@
         <v>2</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
     </row>
     <row r="251" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B251" s="4">
         <v>3</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="252" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B252" s="4">
         <v>4</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>588</v>
+        <v>44</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B253" s="4">
         <v>3</v>
       </c>
       <c r="C253" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B254" s="4">
         <v>3</v>
       </c>
       <c r="C254" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
     </row>
     <row r="255" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B255" s="4">
         <v>3</v>
       </c>
       <c r="C255" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="256" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B256" s="4">
         <v>3</v>
       </c>
       <c r="C256" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="257" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B257" s="4">
         <v>3</v>
       </c>
       <c r="C257" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="258" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6757,68 +6816,68 @@
         <v>2</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
     </row>
     <row r="259" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B259" s="4">
         <v>3</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="260" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B260" s="4">
         <v>4</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>589</v>
+        <v>93</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
     </row>
     <row r="261" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B261" s="4">
         <v>3</v>
       </c>
       <c r="C261" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F261" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:F261" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -6837,15 +6896,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -6855,61 +6914,108 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="B2" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="C2" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>585</v>
       </c>
       <c r="B3" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C3" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="B4" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B5" t="s">
-        <v>585</v>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B6" t="s">
+        <v>590</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>592</v>
+      </c>
+      <c r="B7" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>593</v>
+      </c>
+      <c r="B8" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>594</v>
+      </c>
+      <c r="B9" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B10" t="s">
+        <v>599</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/acn-it/Framework-Nazionale-CS-DP.xlsx
+++ b/tools/excel/acn-it/Framework-Nazionale-CS-DP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\acn-it\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB0603D-6EBB-4F58-81A4-B6E4E6D908A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C4B37F-7F7E-420D-BC9A-A71F40A0647C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="907" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="608">
   <si>
     <t>type</t>
   </si>
@@ -165,9 +165,6 @@
     <t>Gli obiettivi, le capacità e i servizi critici dai quali gli stakeholder dipendono o che si aspettano dall'organizzazione sono compresi e comunicati.</t>
   </si>
   <si>
-    <t>I,E,CONTROLLI,ICONT,ECONT</t>
-  </si>
-  <si>
     <t>GV.OC-04.1</t>
   </si>
   <si>
@@ -310,9 +307,6 @@
   </si>
   <si>
     <t>Nel rispetto delle politiche di cui alla misura GV.PO-01, sono adottate e documentate le procedure in relazione ai punti GV.RR-04.1 e GV.RR-04.2.</t>
-  </si>
-  <si>
-    <t>E,CONTROLLI,ECONT</t>
   </si>
   <si>
     <t>GV.RR-04.4</t>
@@ -1924,16 +1918,25 @@
     <t>REQUISITI</t>
   </si>
   <si>
-    <t>REQUISITI,REQ</t>
-  </si>
-  <si>
-    <t>I,E,REQUISITI,IREQ,EREQ</t>
-  </si>
-  <si>
-    <t>E,REQUISITI,EREQ</t>
-  </si>
-  <si>
     <t xml:space="preserve">No CONT because every controls are either E or I,E </t>
+  </si>
+  <si>
+    <t>== REQ + EREQ</t>
+  </si>
+  <si>
+    <t>== ECONT + ICONT</t>
+  </si>
+  <si>
+    <t>I,E,ICONT,ECONT</t>
+  </si>
+  <si>
+    <t>E,ECONT</t>
+  </si>
+  <si>
+    <t>I,E,IREQ,EREQ</t>
+  </si>
+  <si>
+    <t>E,EREQ</t>
   </si>
 </sst>
 </file>
@@ -2024,7 +2027,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2044,6 +2047,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2349,7 +2353,7 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
     <col min="2" max="2" width="95.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2579,7 +2583,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>36</v>
@@ -2596,7 +2600,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>38</v>
@@ -2613,7 +2617,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>40</v>
@@ -2630,7 +2634,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>42</v>
@@ -2647,13 +2651,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2664,13 +2668,13 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2678,13 +2682,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2695,13 +2699,13 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2712,13 +2716,13 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2729,13 +2733,13 @@
         <v>3</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2746,13 +2750,13 @@
         <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2763,13 +2767,13 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2780,13 +2784,13 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2797,13 +2801,13 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2814,13 +2818,13 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2828,13 +2832,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2845,13 +2849,13 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2862,13 +2866,13 @@
         <v>3</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2879,13 +2883,13 @@
         <v>4</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2896,13 +2900,13 @@
         <v>4</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2913,13 +2917,13 @@
         <v>4</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2930,13 +2934,13 @@
         <v>4</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D25" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2947,13 +2951,13 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2964,13 +2968,13 @@
         <v>3</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2981,13 +2985,13 @@
         <v>4</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2998,13 +3002,13 @@
         <v>4</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3015,13 +3019,13 @@
         <v>4</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3032,13 +3036,13 @@
         <v>4</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3049,13 +3053,13 @@
         <v>4</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3066,13 +3070,13 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3080,13 +3084,13 @@
         <v>2</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3097,13 +3101,13 @@
         <v>3</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3114,13 +3118,13 @@
         <v>4</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3131,13 +3135,13 @@
         <v>4</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3148,13 +3152,13 @@
         <v>4</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3165,13 +3169,13 @@
         <v>3</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3182,13 +3186,13 @@
         <v>4</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3199,13 +3203,13 @@
         <v>4</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3216,13 +3220,13 @@
         <v>4</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3230,13 +3234,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3247,13 +3251,13 @@
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3264,13 +3268,13 @@
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3281,13 +3285,13 @@
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -3295,13 +3299,13 @@
         <v>2</v>
       </c>
       <c r="D47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3312,13 +3316,13 @@
         <v>3</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.3">
@@ -3329,13 +3333,13 @@
         <v>4</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="319.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3346,13 +3350,13 @@
         <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D50" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3363,13 +3367,13 @@
         <v>3</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3380,13 +3384,13 @@
         <v>4</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3397,13 +3401,13 @@
         <v>4</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3414,13 +3418,13 @@
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3431,13 +3435,13 @@
         <v>3</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -3448,13 +3452,13 @@
         <v>4</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3465,13 +3469,13 @@
         <v>3</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3482,13 +3486,13 @@
         <v>4</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3499,13 +3503,13 @@
         <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3516,13 +3520,13 @@
         <v>3</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.3">
@@ -3533,13 +3537,13 @@
         <v>4</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3550,13 +3554,13 @@
         <v>4</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3567,13 +3571,13 @@
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3584,13 +3588,13 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3601,13 +3605,13 @@
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3615,13 +3619,13 @@
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3629,13 +3633,13 @@
         <v>2</v>
       </c>
       <c r="D67" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3646,13 +3650,13 @@
         <v>3</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3663,13 +3667,13 @@
         <v>4</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3680,13 +3684,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3697,13 +3701,13 @@
         <v>4</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3714,13 +3718,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3731,13 +3735,13 @@
         <v>4</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3748,13 +3752,13 @@
         <v>3</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3765,13 +3769,13 @@
         <v>4</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3782,13 +3786,13 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3799,13 +3803,13 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3816,13 +3820,13 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3833,13 +3837,13 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3847,13 +3851,13 @@
         <v>2</v>
       </c>
       <c r="D80" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F80" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3864,13 +3868,13 @@
         <v>3</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3881,13 +3885,13 @@
         <v>4</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -3898,13 +3902,13 @@
         <v>4</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -3915,13 +3919,13 @@
         <v>4</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3932,13 +3936,13 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3949,13 +3953,13 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3966,13 +3970,13 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3983,13 +3987,13 @@
         <v>3</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4000,13 +4004,13 @@
         <v>4</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4017,13 +4021,13 @@
         <v>4</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4034,13 +4038,13 @@
         <v>4</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4051,13 +4055,13 @@
         <v>4</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4068,13 +4072,13 @@
         <v>3</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4085,13 +4089,13 @@
         <v>4</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4102,13 +4106,13 @@
         <v>4</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4119,13 +4123,13 @@
         <v>4</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4136,13 +4140,13 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4153,13 +4157,13 @@
         <v>3</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4170,13 +4174,13 @@
         <v>4</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4187,13 +4191,13 @@
         <v>4</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4204,13 +4208,13 @@
         <v>4</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4221,13 +4225,13 @@
         <v>4</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4238,13 +4242,13 @@
         <v>4</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4255,13 +4259,13 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4272,13 +4276,13 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4289,13 +4293,13 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4303,13 +4307,13 @@
         <v>2</v>
       </c>
       <c r="D107" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F107" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4320,13 +4324,13 @@
         <v>3</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4337,13 +4341,13 @@
         <v>4</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4354,30 +4358,30 @@
         <v>4</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B111" s="4">
+        <v>4</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="B111" s="4">
-        <v>4</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4388,13 +4392,13 @@
         <v>4</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4405,13 +4409,13 @@
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4422,13 +4426,13 @@
         <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4439,13 +4443,13 @@
         <v>3</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.3">
@@ -4456,13 +4460,13 @@
         <v>4</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="127.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4473,13 +4477,13 @@
         <v>4</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -4490,13 +4494,13 @@
         <v>4</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4507,13 +4511,13 @@
         <v>4</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4524,13 +4528,13 @@
         <v>4</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4538,13 +4542,13 @@
         <v>2</v>
       </c>
       <c r="D121" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F121" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4555,13 +4559,13 @@
         <v>3</v>
       </c>
       <c r="C122" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4572,13 +4576,13 @@
         <v>3</v>
       </c>
       <c r="C123" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4589,13 +4593,13 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4606,13 +4610,13 @@
         <v>3</v>
       </c>
       <c r="C125" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4623,13 +4627,13 @@
         <v>3</v>
       </c>
       <c r="C126" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4637,13 +4641,13 @@
         <v>1</v>
       </c>
       <c r="D127" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F127" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -4651,13 +4655,13 @@
         <v>2</v>
       </c>
       <c r="D128" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F128" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4668,13 +4672,13 @@
         <v>3</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4685,13 +4689,13 @@
         <v>4</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4702,13 +4706,13 @@
         <v>4</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4719,13 +4723,13 @@
         <v>4</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4736,13 +4740,13 @@
         <v>4</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4753,13 +4757,13 @@
         <v>3</v>
       </c>
       <c r="C134" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4770,13 +4774,13 @@
         <v>3</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4787,13 +4791,13 @@
         <v>4</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4804,13 +4808,13 @@
         <v>4</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4821,13 +4825,13 @@
         <v>4</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4838,13 +4842,13 @@
         <v>3</v>
       </c>
       <c r="C139" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4855,13 +4859,13 @@
         <v>3</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4872,13 +4876,13 @@
         <v>4</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4889,13 +4893,13 @@
         <v>4</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4906,13 +4910,13 @@
         <v>4</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4923,13 +4927,13 @@
         <v>3</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4940,13 +4944,13 @@
         <v>4</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4957,13 +4961,13 @@
         <v>4</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4971,13 +4975,13 @@
         <v>2</v>
       </c>
       <c r="D147" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="F147" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4988,13 +4992,13 @@
         <v>3</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5005,13 +5009,13 @@
         <v>4</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5022,13 +5026,13 @@
         <v>4</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5039,13 +5043,13 @@
         <v>4</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5056,13 +5060,13 @@
         <v>3</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5073,13 +5077,13 @@
         <v>4</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5090,13 +5094,13 @@
         <v>4</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5104,13 +5108,13 @@
         <v>2</v>
       </c>
       <c r="D155" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F155" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5121,13 +5125,13 @@
         <v>3</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -5138,13 +5142,13 @@
         <v>4</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5155,13 +5159,13 @@
         <v>4</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5172,13 +5176,13 @@
         <v>4</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5189,13 +5193,13 @@
         <v>3</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -5206,13 +5210,13 @@
         <v>4</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5223,13 +5227,13 @@
         <v>4</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5240,13 +5244,13 @@
         <v>3</v>
       </c>
       <c r="C163" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5257,13 +5261,13 @@
         <v>3</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5274,13 +5278,13 @@
         <v>4</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5291,13 +5295,13 @@
         <v>4</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5308,13 +5312,13 @@
         <v>4</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5325,13 +5329,13 @@
         <v>4</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5342,13 +5346,13 @@
         <v>4</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5356,13 +5360,13 @@
         <v>2</v>
       </c>
       <c r="D170" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F170" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="E170" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F170" s="3" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5373,13 +5377,13 @@
         <v>3</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5390,13 +5394,13 @@
         <v>4</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5407,13 +5411,13 @@
         <v>4</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5424,13 +5428,13 @@
         <v>3</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5441,13 +5445,13 @@
         <v>4</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5458,13 +5462,13 @@
         <v>4</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5475,13 +5479,13 @@
         <v>4</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5492,13 +5496,13 @@
         <v>4</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5509,13 +5513,13 @@
         <v>4</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5526,13 +5530,13 @@
         <v>3</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5543,13 +5547,13 @@
         <v>4</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5560,13 +5564,13 @@
         <v>4</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5577,13 +5581,13 @@
         <v>3</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5594,13 +5598,13 @@
         <v>4</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5611,13 +5615,13 @@
         <v>4</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5628,13 +5632,13 @@
         <v>4</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5645,13 +5649,13 @@
         <v>4</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5662,13 +5666,13 @@
         <v>3</v>
       </c>
       <c r="C188" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5679,13 +5683,13 @@
         <v>3</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5696,13 +5700,13 @@
         <v>4</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5710,13 +5714,13 @@
         <v>2</v>
       </c>
       <c r="D191" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F191" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="F191" s="3" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5727,13 +5731,13 @@
         <v>3</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5744,13 +5748,13 @@
         <v>4</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5761,13 +5765,13 @@
         <v>4</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5778,13 +5782,13 @@
         <v>4</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5795,13 +5799,13 @@
         <v>4</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5812,13 +5816,13 @@
         <v>3</v>
       </c>
       <c r="C197" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5829,13 +5833,13 @@
         <v>3</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5846,13 +5850,13 @@
         <v>4</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5863,13 +5867,13 @@
         <v>4</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5880,13 +5884,13 @@
         <v>3</v>
       </c>
       <c r="C201" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5894,13 +5898,13 @@
         <v>1</v>
       </c>
       <c r="D202" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F202" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5908,13 +5912,13 @@
         <v>2</v>
       </c>
       <c r="D203" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="F203" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="E203" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="F203" s="3" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5925,13 +5929,13 @@
         <v>3</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5942,13 +5946,13 @@
         <v>4</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5959,13 +5963,13 @@
         <v>4</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5976,13 +5980,13 @@
         <v>4</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5993,13 +5997,13 @@
         <v>4</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6010,13 +6014,13 @@
         <v>4</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6027,13 +6031,13 @@
         <v>4</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6044,13 +6048,13 @@
         <v>4</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6061,13 +6065,13 @@
         <v>3</v>
       </c>
       <c r="C212" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6078,13 +6082,13 @@
         <v>3</v>
       </c>
       <c r="C213" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6095,13 +6099,13 @@
         <v>3</v>
       </c>
       <c r="C214" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6112,13 +6116,13 @@
         <v>3</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6129,13 +6133,13 @@
         <v>4</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6146,13 +6150,13 @@
         <v>4</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6160,13 +6164,13 @@
         <v>2</v>
       </c>
       <c r="D218" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F218" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="F218" s="3" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6177,13 +6181,13 @@
         <v>3</v>
       </c>
       <c r="C219" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6194,13 +6198,13 @@
         <v>3</v>
       </c>
       <c r="C220" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6211,13 +6215,13 @@
         <v>3</v>
       </c>
       <c r="C221" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6228,13 +6232,13 @@
         <v>3</v>
       </c>
       <c r="C222" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6245,13 +6249,13 @@
         <v>3</v>
       </c>
       <c r="C223" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6262,13 +6266,13 @@
         <v>3</v>
       </c>
       <c r="C224" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6276,13 +6280,13 @@
         <v>1</v>
       </c>
       <c r="D225" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="F225" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6290,13 +6294,13 @@
         <v>2</v>
       </c>
       <c r="D226" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="F226" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="F226" s="3" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6307,13 +6311,13 @@
         <v>3</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="130.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -6324,13 +6328,13 @@
         <v>4</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6341,13 +6345,13 @@
         <v>4</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6358,13 +6362,13 @@
         <v>4</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6375,13 +6379,13 @@
         <v>3</v>
       </c>
       <c r="C231" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6392,13 +6396,13 @@
         <v>3</v>
       </c>
       <c r="C232" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6409,13 +6413,13 @@
         <v>3</v>
       </c>
       <c r="C233" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6426,13 +6430,13 @@
         <v>3</v>
       </c>
       <c r="C234" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6440,13 +6444,13 @@
         <v>2</v>
       </c>
       <c r="D235" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="F235" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="E235" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="F235" s="3" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="236" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6457,13 +6461,13 @@
         <v>3</v>
       </c>
       <c r="C236" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6474,13 +6478,13 @@
         <v>3</v>
       </c>
       <c r="C237" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6491,13 +6495,13 @@
         <v>3</v>
       </c>
       <c r="C238" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="239" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6508,13 +6512,13 @@
         <v>3</v>
       </c>
       <c r="C239" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6522,13 +6526,13 @@
         <v>2</v>
       </c>
       <c r="D240" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="F240" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="E240" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="F240" s="3" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="241" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6539,13 +6543,13 @@
         <v>3</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="242" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6556,13 +6560,13 @@
         <v>4</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6573,13 +6577,13 @@
         <v>4</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6590,13 +6594,13 @@
         <v>3</v>
       </c>
       <c r="C244" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="245" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6607,13 +6611,13 @@
         <v>3</v>
       </c>
       <c r="C245" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="246" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6621,13 +6625,13 @@
         <v>2</v>
       </c>
       <c r="D246" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="F246" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="F246" s="3" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6638,13 +6642,13 @@
         <v>3</v>
       </c>
       <c r="C247" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6655,13 +6659,13 @@
         <v>3</v>
       </c>
       <c r="C248" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="249" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6669,13 +6673,13 @@
         <v>1</v>
       </c>
       <c r="D249" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="250" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6683,13 +6687,13 @@
         <v>2</v>
       </c>
       <c r="D250" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="F250" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="E250" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="F250" s="3" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="251" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6700,13 +6704,13 @@
         <v>3</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="252" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6717,13 +6721,13 @@
         <v>4</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>44</v>
+        <v>604</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6734,13 +6738,13 @@
         <v>3</v>
       </c>
       <c r="C253" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6751,13 +6755,13 @@
         <v>3</v>
       </c>
       <c r="C254" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="255" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6768,13 +6772,13 @@
         <v>3</v>
       </c>
       <c r="C255" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="256" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6785,13 +6789,13 @@
         <v>3</v>
       </c>
       <c r="C256" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="257" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6802,13 +6806,13 @@
         <v>3</v>
       </c>
       <c r="C257" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="258" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6816,13 +6820,13 @@
         <v>2</v>
       </c>
       <c r="D258" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="F258" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="259" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6833,13 +6837,13 @@
         <v>3</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="260" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6850,13 +6854,13 @@
         <v>4</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>93</v>
+        <v>605</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="261" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6867,13 +6871,13 @@
         <v>3</v>
       </c>
       <c r="C261" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -6914,16 +6918,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.21875" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -6934,59 +6940,77 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C2" t="s">
         <v>582</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>583</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>585</v>
       </c>
-      <c r="B3" t="s">
-        <v>586</v>
-      </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>586</v>
+      </c>
+      <c r="B4" t="s">
+        <v>598</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>590</v>
+      </c>
+      <c r="B5" t="s">
+        <v>594</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>602</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="E5" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B6" t="s">
+        <v>595</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>588</v>
-      </c>
-      <c r="B5" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>589</v>
-      </c>
-      <c r="B6" t="s">
-        <v>590</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>591</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>592</v>
       </c>
@@ -6994,28 +7018,12 @@
         <v>596</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>593</v>
       </c>
       <c r="B8" t="s">
         <v>597</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>594</v>
-      </c>
-      <c r="B9" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>595</v>
-      </c>
-      <c r="B10" t="s">
-        <v>599</v>
       </c>
     </row>
   </sheetData>
